--- a/VerveStacks_NGA_grids_kan10/SuppXLS/Scen_Par-AR6_R10.xlsx
+++ b/VerveStacks_NGA_grids_kan10/SuppXLS/Scen_Par-AR6_R10.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_NGA_grids_kan10\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{623CD81D-3D6F-4705-9CD2-FBD004E57228}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F8BAF0E-E4DC-44C4-94DD-551E47AE4395}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_NGA_grids_kan10/SuppXLS/Scen_Par-AR6_R10.xlsx
+++ b/VerveStacks_NGA_grids_kan10/SuppXLS/Scen_Par-AR6_R10.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_NGA_grids_kan10\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F8BAF0E-E4DC-44C4-94DD-551E47AE4395}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BC440A0-0BA4-45D2-8A7F-31A3C1B57F36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6067,7 +6067,7 @@
         <v>82</v>
       </c>
       <c r="O4" s="10" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:39" x14ac:dyDescent="0.45">
